--- a/Utah_Jazz_2025-26_stats.xlsx
+++ b/Utah_Jazz_2025-26_stats.xlsx
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L13" t="n">
         <v>8</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>9</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -3641,31 +3641,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.454545454545455</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.75</v>
+        <v>8.454545454545455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.545454545454546</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.545454545454545</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.727272727272727</v>
+        <v>3.833333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -4169,31 +4169,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="10">
